--- a/artfynd/A 51767-2019 artfynd.xlsx
+++ b/artfynd/A 51767-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124243570</v>
+        <v>124243562</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735906</v>
+        <v>735629</v>
       </c>
       <c r="R2" t="n">
-        <v>7065330</v>
+        <v>7065860</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124243569</v>
+        <v>124243570</v>
       </c>
       <c r="B3" t="n">
         <v>92293</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735776</v>
+        <v>735906</v>
       </c>
       <c r="R3" t="n">
-        <v>7065430</v>
+        <v>7065330</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124243562</v>
+        <v>124243567</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735629</v>
+        <v>735783</v>
       </c>
       <c r="R4" t="n">
-        <v>7065860</v>
+        <v>7065450</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -962,6 +962,11 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>torrträd</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -970,6 +975,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -986,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124243567</v>
+        <v>124243569</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1018,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735783</v>
+        <v>735776</v>
       </c>
       <c r="R5" t="n">
-        <v>7065450</v>
+        <v>7065430</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1064,11 +1084,6 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>torrträd</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1077,21 +1092,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 51767-2019 artfynd.xlsx
+++ b/artfynd/A 51767-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124243562</v>
+        <v>124243567</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735629</v>
+        <v>735783</v>
       </c>
       <c r="R2" t="n">
-        <v>7065860</v>
+        <v>7065450</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -758,6 +753,11 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>torrträd</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,6 +766,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -884,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124243567</v>
+        <v>124243562</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735783</v>
+        <v>735629</v>
       </c>
       <c r="R4" t="n">
-        <v>7065450</v>
+        <v>7065860</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -962,11 +982,6 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>torrträd</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -975,21 +990,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 51767-2019 artfynd.xlsx
+++ b/artfynd/A 51767-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124243567</v>
+        <v>124243569</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735783</v>
+        <v>735776</v>
       </c>
       <c r="R2" t="n">
-        <v>7065450</v>
+        <v>7065430</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,11 +753,6 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>torrträd</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,21 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -1006,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124243569</v>
+        <v>124243567</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735776</v>
+        <v>735783</v>
       </c>
       <c r="R5" t="n">
-        <v>7065430</v>
+        <v>7065450</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1084,6 +1064,11 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>torrträd</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1092,6 +1077,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 51767-2019 artfynd.xlsx
+++ b/artfynd/A 51767-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124243569</v>
+        <v>124243562</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735776</v>
+        <v>735629</v>
       </c>
       <c r="R2" t="n">
-        <v>7065430</v>
+        <v>7065860</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124243562</v>
+        <v>124243569</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,43 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735629</v>
+        <v>735776</v>
       </c>
       <c r="R4" t="n">
-        <v>7065860</v>
+        <v>7065430</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 51767-2019 artfynd.xlsx
+++ b/artfynd/A 51767-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124243562</v>
+        <v>124243570</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>92293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735629</v>
+        <v>735906</v>
       </c>
       <c r="R2" t="n">
-        <v>7065860</v>
+        <v>7065330</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124243570</v>
+        <v>124243569</v>
       </c>
       <c r="B3" t="n">
         <v>92293</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735906</v>
+        <v>735776</v>
       </c>
       <c r="R3" t="n">
-        <v>7065330</v>
+        <v>7065430</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124243569</v>
+        <v>124243567</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735776</v>
+        <v>735783</v>
       </c>
       <c r="R4" t="n">
-        <v>7065430</v>
+        <v>7065450</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -962,6 +957,11 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>torrträd</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -970,6 +970,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -986,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124243567</v>
+        <v>124243562</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +1017,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735783</v>
+        <v>735629</v>
       </c>
       <c r="R5" t="n">
-        <v>7065450</v>
+        <v>7065860</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1064,11 +1084,6 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>torrträd</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1077,21 +1092,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 51767-2019 artfynd.xlsx
+++ b/artfynd/A 51767-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124243570</v>
+        <v>124243569</v>
       </c>
       <c r="B2" t="n">
         <v>92293</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735906</v>
+        <v>735776</v>
       </c>
       <c r="R2" t="n">
-        <v>7065330</v>
+        <v>7065430</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124243569</v>
+        <v>124243562</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735776</v>
+        <v>735629</v>
       </c>
       <c r="R3" t="n">
-        <v>7065430</v>
+        <v>7065860</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124243567</v>
+        <v>124243570</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735783</v>
+        <v>735906</v>
       </c>
       <c r="R4" t="n">
-        <v>7065450</v>
+        <v>7065330</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -957,11 +962,6 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>torrträd</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -970,21 +970,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1001,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124243562</v>
+        <v>124243567</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,39 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735629</v>
+        <v>735783</v>
       </c>
       <c r="R5" t="n">
-        <v>7065860</v>
+        <v>7065450</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1084,6 +1064,11 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>torrträd</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1092,6 +1077,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 51767-2019 artfynd.xlsx
+++ b/artfynd/A 51767-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124243569</v>
+        <v>124243570</v>
       </c>
       <c r="B2" t="n">
         <v>92293</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735776</v>
+        <v>735906</v>
       </c>
       <c r="R2" t="n">
-        <v>7065430</v>
+        <v>7065330</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124243570</v>
+        <v>124243569</v>
       </c>
       <c r="B4" t="n">
         <v>92293</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735906</v>
+        <v>735776</v>
       </c>
       <c r="R4" t="n">
-        <v>7065330</v>
+        <v>7065430</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 51767-2019 artfynd.xlsx
+++ b/artfynd/A 51767-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124243570</v>
+        <v>124243562</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735906</v>
+        <v>735629</v>
       </c>
       <c r="R2" t="n">
-        <v>7065330</v>
+        <v>7065860</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124243562</v>
+        <v>124243570</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735629</v>
+        <v>735906</v>
       </c>
       <c r="R3" t="n">
-        <v>7065860</v>
+        <v>7065330</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 51767-2019 artfynd.xlsx
+++ b/artfynd/A 51767-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124243562</v>
+        <v>124243570</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>92293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735629</v>
+        <v>735906</v>
       </c>
       <c r="R2" t="n">
-        <v>7065860</v>
+        <v>7065330</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124243570</v>
+        <v>124243569</v>
       </c>
       <c r="B3" t="n">
         <v>92293</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735906</v>
+        <v>735776</v>
       </c>
       <c r="R3" t="n">
-        <v>7065330</v>
+        <v>7065430</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124243569</v>
+        <v>124243562</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +891,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735776</v>
+        <v>735629</v>
       </c>
       <c r="R4" t="n">
-        <v>7065430</v>
+        <v>7065860</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 51767-2019 artfynd.xlsx
+++ b/artfynd/A 51767-2019 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124243569</v>
+        <v>124243567</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735776</v>
+        <v>735783</v>
       </c>
       <c r="R3" t="n">
-        <v>7065430</v>
+        <v>7065450</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -855,6 +855,11 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>torrträd</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -863,6 +868,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124243562</v>
+        <v>124243569</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,43 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735629</v>
+        <v>735776</v>
       </c>
       <c r="R4" t="n">
-        <v>7065860</v>
+        <v>7065430</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124243567</v>
+        <v>124243562</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +1017,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ängersjö, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735783</v>
+        <v>735629</v>
       </c>
       <c r="R5" t="n">
-        <v>7065450</v>
+        <v>7065860</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1064,11 +1084,6 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>torrträd</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1077,21 +1092,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
